--- a/public/dropvine-pricing-calculator.xlsx
+++ b/public/dropvine-pricing-calculator.xlsx
@@ -22,30 +22,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">🍞  What Should I Charge?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A friendly pricing calculator for makers, bakers &amp; small-batch sellers — by Dropvine</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
+  <si>
+    <t xml:space="preserve">What Should I Charge?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A practical pricing calculator for makers, bakers, and small-batch sellers — by Dropvine</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">Open the "Pricing Your Time" tab first if you're not sure what to charge for your labor.</t>
+    <t xml:space="preserve">Open the "Pricing Your Time" tab first if you are not sure what to charge for your labor.</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Go to "Pricing Calculator" and fill in your costs for each product — ingredients, packaging, and labor.</t>
+    <t xml:space="preserve">Go to "Pricing Calculator" and fill in your costs — ingredients, packaging, and labor.</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">Set your buffer (a cushion for waste/overhead) and your target margin — how much profit you want to keep.</t>
+    <t xml:space="preserve">Set your buffer (a cushion for waste and overhead) and your target margin.</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
@@ -54,49 +54,190 @@
     <t xml:space="preserve">Your suggested price fills in automatically. Round it to a clean number before you post it.</t>
   </si>
   <si>
-    <t xml:space="preserve">💡  Three examples are already filled in — a bakery item, a ceramics piece, and a workshop seat — so you can see it working before you touch anything.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🌱  Made with love by Dropvine — the pre-order tool for independent makers · dropvine.pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⏱  What's Your Time Worth?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The hardest number to name — and the most important one to get right.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hands-on time vs. waiting time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active / hands-on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decorating, kneading, throwing on the wheel, teaching, cutting, assembling — time only you can give.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive / waiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dough rising, kiln firing, cooling, curing — time the product needs but your hands don't. Charge less for this (or not at all).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Figure out your hourly rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What would you pay someone else to do this job?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What do you need to earn per hour to feel good about it?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ Your labor rate (enter it in the Pricing Calculator):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🌱  Built by Dropvine — dropvine.pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🍞 🏺 ✂️  Pricing Calculator</t>
+    <t xml:space="preserve">Three examples are already filled in — a bakery item, a ceramics piece, and a workshop seat — so you can see it working before you touch anything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made with care by Dropvine — the pre-order tool for independent makers · dropvine.pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Is Your Time Worth?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your labor rate is the most important number in the Pricing Calculator — and the one most makers skip or underestimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 1 — Hands-on time vs. waiting time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not all time in your product is equal. Separate it before you estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it means</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands-on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time only you can give. Your hands are actively working.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kneading dough, decorating, throwing on the wheel, teaching a class, cutting fabric, assembling jewelry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge your full hourly rate for every minute of this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The product needs time, but your hands are free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dough rising, kiln firing, candles cooling, resin curing, bread baking in the oven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge a fraction of your rate (25-50%) or nothing — your time is not fully consumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked example: sourdough loaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clock time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billable hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixing and shaping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 hrs charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not charged (hands free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folding (4x, 30 sec each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring and loading oven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooling and packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total billable labor hours per loaf:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At $20/hr, that is $10.43 in labor — not 2 or 3 hours worth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 2 — Figure out your hourly rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your rate should sit between what you would pay someone else and what you need to feel good about your time. Answer these two questions first, then pick a number between them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What would you pay a skilled person to do this job?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you hired a baker, ceramicist, or instructor to do exactly what you do, what would you pay them per hour? This is your floor. You should never value your own skilled time below what you would pay someone else for the same work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: A skilled baker earns $18-24/hr. A pottery studio assistant $16-22/hr. A skilled seamstress $20-30/hr. A fitness or wellness instructor $25-45/hr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What do you need to earn to feel good about this?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is personal, not mathematical. What hourly rate makes the work feel worthwhile — not just profitable, but worth your time and energy? If you feel resentful doing a 2-hour batch for $20, your rate is too low. That feeling is real data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: Most small makers land between $18-35/hr for hands-on production work. Workshop instructors often set $30-50/hr. There is no wrong answer — only one that does or does not make the work sustainable for you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your labor rate — enter this number in the Pricing Calculator:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick a number between those two that feels honest. Use the same rate for all your products, or vary it by skill level (e.g. a higher rate for decorated items than plain ones). This goes in the Labor Rate column on the Pricing Calculator tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: Quick starting point: take the annual income you want to earn from this work, divide by 2,000 hours (a standard work year). That gives you your minimum hourly rate. Example: $40,000 / 2,000 = $20/hr minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What would you pay someone else? ($/hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What do you need to earn? ($/hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your labor rate (enter this in Pricing Calculator):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built by Dropvine — dropvine.pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing Calculator</t>
   </si>
   <si>
     <t xml:space="preserve">YOUR COSTS</t>
@@ -149,16 +290,16 @@
 Check</t>
   </si>
   <si>
-    <t xml:space="preserve">🍞  Sourdough Loaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏺  Ceramic Mug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✂️  Workshop Seat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold cells are your assumptions — buffer % and margin %. See "Start Here" for guidance. Not sure about your rate? Check the "Pricing Your Time" tab.  🌱  Dropvine — dropvine.pro</t>
+    <t xml:space="preserve">Sourdough Loaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceramic Mug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop Seat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold cells are your assumptions — buffer % and margin %. See Start Here for guidance. Not sure about your rate? Check the Pricing Your Time tab.  Built by Dropvine — dropvine.pro</t>
   </si>
 </sst>
 </file>
@@ -171,7 +312,7 @@
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +384,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="20"/>
-      <color rgb="FF1B3A6B"/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -259,7 +400,37 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF3F6B4A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3A3630"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF3A3630"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF3F6B4A"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -274,15 +445,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1450D6"/>
+      <sz val="10"/>
+      <color rgb="FF8A5A2B"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="18"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -297,8 +468,62 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF8C8478"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF3A3630"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF3F6B4A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF8A5A2B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF8A5A2B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1B3A6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1450D6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
       <color rgb="FF8A5A2B"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -337,7 +562,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,8 +595,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFD4"/>
-        <bgColor rgb="FFF3ECE0"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFBF6EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -382,8 +607,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFBF6EE"/>
+        <fgColor rgb="FFE7ECF3"/>
+        <bgColor rgb="FFF3ECE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFD4"/>
+        <bgColor rgb="FFF3ECE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -430,7 +661,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -463,99 +694,207 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="28" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="27" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="27" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -563,15 +902,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -605,7 +944,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFCEFD4"/>
-      <rgbColor rgb="FFFBF6EE"/>
+      <rgbColor rgb="FFE7ECF3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1450D6"/>
@@ -619,9 +958,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFFBF6EE"/>
+      <rgbColor rgb="FFDCE8D8"/>
       <rgbColor rgb="FFF3ECE0"/>
-      <rgbColor rgb="FFDCE8D8"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -872,148 +1211,148 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
@@ -1024,19 +1363,19 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1045,13 +1384,13 @@
       <c r="G21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
@@ -1063,24 +1402,24 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
@@ -1399,18 +1738,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:G9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:G12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:G15"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:G18"/>
-    <mergeCell ref="A21:G22"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:G11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:G17"/>
+    <mergeCell ref="A20:G21"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1427,31 +1766,35 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8"/>
@@ -1461,17 +1804,19 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
@@ -1481,6 +1826,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
@@ -1490,8 +1836,9 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
@@ -1501,6 +1848,7 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
@@ -1510,59 +1858,83 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="D11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
@@ -1572,133 +1944,227 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="C18" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+    </row>
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
@@ -1708,15 +2174,19 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
@@ -1726,6 +2196,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
@@ -1735,33 +2206,43 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+    </row>
+    <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+    </row>
+    <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1"/>
@@ -1771,33 +2252,43 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+    </row>
+    <row r="37" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+    </row>
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1"/>
@@ -1807,30 +2298,667 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+    </row>
+    <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:G13"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A26:G26"/>
+  <mergeCells count="33">
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1865,48 +2993,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
+      <c r="A1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
@@ -1924,388 +3052,388 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="B5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="B5" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>38</v>
+      <c r="A6" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="48" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="A7" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="50" t="n">
         <v>2.75</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="50" t="n">
         <v>0.35</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="52" t="n">
         <f aca="false">IF(D7="","",D7*E7)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="52" t="n">
         <f aca="false">IF(B7="","",(B7+C7+F7)*(1+G7))</f>
         <v>8.91</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="53" t="n">
         <v>0.3</v>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J7" s="54" t="n">
         <f aca="false">IF(OR(H7="",I7=1),"",H7/(1-I7))</f>
         <v>12.7285714285714</v>
       </c>
-      <c r="K7" s="25" t="n">
+      <c r="K7" s="52" t="n">
         <f aca="false">IF(J7="","",J7-H7)</f>
         <v>3.81857142857143</v>
       </c>
-      <c r="L7" s="28" t="n">
+      <c r="L7" s="55" t="n">
         <f aca="false">IF(OR(J7="",J7=0),"",K7/J7)</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="30" t="n">
+      <c r="A8" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="57" t="n">
         <v>0.75</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="58" t="n">
         <v>0.75</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="57" t="n">
         <v>24</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="59" t="n">
         <f aca="false">IF(D8="","",D8*E8)</f>
         <v>18</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="59" t="n">
         <f aca="false">IF(B8="","",(B8+C8+F8)*(1+G8))</f>
         <v>25.025</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="53" t="n">
         <v>0.35</v>
       </c>
-      <c r="J8" s="33" t="n">
+      <c r="J8" s="60" t="n">
         <f aca="false">IF(OR(H8="",I8=1),"",H8/(1-I8))</f>
         <v>38.5</v>
       </c>
-      <c r="K8" s="32" t="n">
+      <c r="K8" s="59" t="n">
         <f aca="false">IF(J8="","",J8-H8)</f>
         <v>13.475</v>
       </c>
-      <c r="L8" s="34" t="n">
+      <c r="L8" s="61" t="n">
         <f aca="false">IF(OR(J8="",J8=0),"",K8/J8)</f>
         <v>0.35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="23" t="n">
+      <c r="A9" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="50" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="52" t="n">
         <f aca="false">IF(D9="","",D9*E9)</f>
         <v>22.5</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="53" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="52" t="n">
         <f aca="false">IF(B9="","",(B9+C9+F9)*(1+G9))</f>
         <v>32.025</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="53" t="n">
         <v>0.35</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="54" t="n">
         <f aca="false">IF(OR(H9="",I9=1),"",H9/(1-I9))</f>
         <v>49.2692307692308</v>
       </c>
-      <c r="K9" s="25" t="n">
+      <c r="K9" s="52" t="n">
         <f aca="false">IF(J9="","",J9-H9)</f>
         <v>17.2442307692308</v>
       </c>
-      <c r="L9" s="28" t="n">
+      <c r="L9" s="55" t="n">
         <f aca="false">IF(OR(J9="",J9=0),"",K9/J9)</f>
         <v>0.35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="32" t="str">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="59" t="str">
         <f aca="false">IF(D10="","",D10*E10)</f>
         <v/>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="32" t="str">
+      <c r="G10" s="53"/>
+      <c r="H10" s="59" t="str">
         <f aca="false">IF(B10="","",(B10+C10+F10)*(1+G10))</f>
         <v/>
       </c>
-      <c r="I10" s="26"/>
-      <c r="J10" s="33" t="str">
+      <c r="I10" s="53"/>
+      <c r="J10" s="60" t="str">
         <f aca="false">IF(OR(H10="",I10=1),"",H10/(1-I10))</f>
         <v/>
       </c>
-      <c r="K10" s="32" t="str">
+      <c r="K10" s="59" t="str">
         <f aca="false">IF(J10="","",J10-H10)</f>
         <v/>
       </c>
-      <c r="L10" s="34" t="str">
+      <c r="L10" s="61" t="str">
         <f aca="false">IF(OR(J10="",J10=0),"",K10/J10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="25" t="str">
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="52" t="str">
         <f aca="false">IF(D11="","",D11*E11)</f>
         <v/>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="25" t="str">
+      <c r="G11" s="53"/>
+      <c r="H11" s="52" t="str">
         <f aca="false">IF(B11="","",(B11+C11+F11)*(1+G11))</f>
         <v/>
       </c>
-      <c r="I11" s="26"/>
-      <c r="J11" s="27" t="str">
+      <c r="I11" s="53"/>
+      <c r="J11" s="54" t="str">
         <f aca="false">IF(OR(H11="",I11=1),"",H11/(1-I11))</f>
         <v/>
       </c>
-      <c r="K11" s="25" t="str">
+      <c r="K11" s="52" t="str">
         <f aca="false">IF(J11="","",J11-H11)</f>
         <v/>
       </c>
-      <c r="L11" s="28" t="str">
+      <c r="L11" s="55" t="str">
         <f aca="false">IF(OR(J11="",J11=0),"",K11/J11)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="32" t="str">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="59" t="str">
         <f aca="false">IF(D12="","",D12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="32" t="str">
+      <c r="G12" s="53"/>
+      <c r="H12" s="59" t="str">
         <f aca="false">IF(B12="","",(B12+C12+F12)*(1+G12))</f>
         <v/>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="33" t="str">
+      <c r="I12" s="53"/>
+      <c r="J12" s="60" t="str">
         <f aca="false">IF(OR(H12="",I12=1),"",H12/(1-I12))</f>
         <v/>
       </c>
-      <c r="K12" s="32" t="str">
+      <c r="K12" s="59" t="str">
         <f aca="false">IF(J12="","",J12-H12)</f>
         <v/>
       </c>
-      <c r="L12" s="34" t="str">
+      <c r="L12" s="61" t="str">
         <f aca="false">IF(OR(J12="",J12=0),"",K12/J12)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="25" t="str">
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="52" t="str">
         <f aca="false">IF(D13="","",D13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="25" t="str">
+      <c r="G13" s="53"/>
+      <c r="H13" s="52" t="str">
         <f aca="false">IF(B13="","",(B13+C13+F13)*(1+G13))</f>
         <v/>
       </c>
-      <c r="I13" s="26"/>
-      <c r="J13" s="27" t="str">
+      <c r="I13" s="53"/>
+      <c r="J13" s="54" t="str">
         <f aca="false">IF(OR(H13="",I13=1),"",H13/(1-I13))</f>
         <v/>
       </c>
-      <c r="K13" s="25" t="str">
+      <c r="K13" s="52" t="str">
         <f aca="false">IF(J13="","",J13-H13)</f>
         <v/>
       </c>
-      <c r="L13" s="28" t="str">
+      <c r="L13" s="55" t="str">
         <f aca="false">IF(OR(J13="",J13=0),"",K13/J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="32" t="str">
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="59" t="str">
         <f aca="false">IF(D14="","",D14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="32" t="str">
+      <c r="G14" s="53"/>
+      <c r="H14" s="59" t="str">
         <f aca="false">IF(B14="","",(B14+C14+F14)*(1+G14))</f>
         <v/>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="33" t="str">
+      <c r="I14" s="53"/>
+      <c r="J14" s="60" t="str">
         <f aca="false">IF(OR(H14="",I14=1),"",H14/(1-I14))</f>
         <v/>
       </c>
-      <c r="K14" s="32" t="str">
+      <c r="K14" s="59" t="str">
         <f aca="false">IF(J14="","",J14-H14)</f>
         <v/>
       </c>
-      <c r="L14" s="34" t="str">
+      <c r="L14" s="61" t="str">
         <f aca="false">IF(OR(J14="",J14=0),"",K14/J14)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="25" t="str">
+      <c r="A15" s="49"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="52" t="str">
         <f aca="false">IF(D15="","",D15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="25" t="str">
+      <c r="G15" s="53"/>
+      <c r="H15" s="52" t="str">
         <f aca="false">IF(B15="","",(B15+C15+F15)*(1+G15))</f>
         <v/>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27" t="str">
+      <c r="I15" s="53"/>
+      <c r="J15" s="54" t="str">
         <f aca="false">IF(OR(H15="",I15=1),"",H15/(1-I15))</f>
         <v/>
       </c>
-      <c r="K15" s="25" t="str">
+      <c r="K15" s="52" t="str">
         <f aca="false">IF(J15="","",J15-H15)</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="str">
+      <c r="L15" s="55" t="str">
         <f aca="false">IF(OR(J15="",J15=0),"",K15/J15)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="32" t="str">
+      <c r="A16" s="56"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="59" t="str">
         <f aca="false">IF(D16="","",D16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="32" t="str">
+      <c r="G16" s="53"/>
+      <c r="H16" s="59" t="str">
         <f aca="false">IF(B16="","",(B16+C16+F16)*(1+G16))</f>
         <v/>
       </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="33" t="str">
+      <c r="I16" s="53"/>
+      <c r="J16" s="60" t="str">
         <f aca="false">IF(OR(H16="",I16=1),"",H16/(1-I16))</f>
         <v/>
       </c>
-      <c r="K16" s="32" t="str">
+      <c r="K16" s="59" t="str">
         <f aca="false">IF(J16="","",J16-H16)</f>
         <v/>
       </c>
-      <c r="L16" s="34" t="str">
+      <c r="L16" s="61" t="str">
         <f aca="false">IF(OR(J16="",J16=0),"",K16/J16)</f>
         <v/>
       </c>
@@ -2339,20 +3467,20 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
+      <c r="A19" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
